--- a/dist/Datas/Log/Log_export.xlsx
+++ b/dist/Datas/Log/Log_export.xlsx
@@ -517,27 +517,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13402</v>
+        <v>15623</v>
       </c>
       <c r="B2" t="n">
-        <v>908</v>
+        <v>691</v>
       </c>
       <c r="C2" t="n">
         <v>300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Hervé</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DOYEN</t>
+          <t>ARRIBART</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomas.Doyen@fr.toyota-industries.eu</t>
+          <t>Herve.Arribart@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -547,32 +547,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1404-T2-TE-49</t>
+          <t>1404-T2-TE-35</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - RRE H et RRE H2</t>
+          <t>BUSSY 2025 - VECTOR A</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>2192</v>
+        <v>1984</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -590,27 +590,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13579</v>
+        <v>17694</v>
       </c>
       <c r="B3" t="n">
-        <v>908</v>
+        <v>691</v>
       </c>
       <c r="C3" t="n">
         <v>300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alexis</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LONGNY</t>
+          <t>ALMEIDA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Alexis.LONGNY@fr.toyota-industries.eu</t>
+          <t>Maxime.Almeida@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -620,32 +620,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1404-T2-TE-49</t>
+          <t>1404-T2-TE-35</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - RRE H et RRE H2</t>
+          <t>BUSSY 2025 - VECTOR A</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>2192</v>
+        <v>1984</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -663,62 +663,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17955</v>
+        <v>18929</v>
       </c>
       <c r="B4" t="n">
-        <v>908</v>
+        <v>691</v>
       </c>
       <c r="C4" t="n">
         <v>300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Maxence</t>
+          <t>Sylvain</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>POTIRON</t>
+          <t>Hurte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maxence.POTIRON@fr.toyota-industries.eu</t>
+          <t>Sylvain.Hurte@ch.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Toyota Material Handling France S.A.S.</t>
+          <t>Toyota Material Handling Schweiz AG</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1404-T2-TE-49</t>
+          <t>1404-T2-TE-35</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - RRE H et RRE H2</t>
+          <t>BUSSY 2025 - VECTOR A</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>2192</v>
+        <v>1984</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -736,62 +736,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16788</v>
+        <v>17341</v>
       </c>
       <c r="B5" t="n">
-        <v>908</v>
+        <v>691</v>
       </c>
       <c r="C5" t="n">
         <v>300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Léo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BLENO</t>
+          <t>SANNA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>kbleno.axxel@gmail.com</t>
+          <t>Leo.Sanna@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AXXEL MANUTENTION</t>
+          <t>Toyota Material Handling France S.A.S.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1404-T2-TE-49</t>
+          <t>1404-T2-TE-35</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - RRE H et RRE H2</t>
+          <t>BUSSY 2025 - VECTOR A</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>2192</v>
+        <v>1984</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -809,27 +809,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13551</v>
+        <v>17622</v>
       </c>
       <c r="B6" t="n">
-        <v>908</v>
+        <v>691</v>
       </c>
       <c r="C6" t="n">
         <v>300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cyril</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AUMONT</t>
+          <t>QUENTIN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cyril.Aumont@fr.toyota-industries.eu</t>
+          <t>Nicolas.QUENTIN@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -839,32 +839,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1404-T2-TE-49</t>
+          <t>1404-T2-TE-35</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - RRE H et RRE H2</t>
+          <t>BUSSY 2025 - VECTOR A</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>2192</v>
+        <v>1984</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -882,27 +882,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17534</v>
+        <v>17440</v>
       </c>
       <c r="B7" t="n">
-        <v>908</v>
+        <v>691</v>
       </c>
       <c r="C7" t="n">
         <v>300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Matthieu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BIN</t>
+          <t>PAPETTI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bruno.Bin@fr.toyota-industries.eu</t>
+          <t>Matthieu.Papetti@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -912,32 +912,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RRE H et RRE H2</t>
+          <t>VECTOR A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1404-T2-TE-49</t>
+          <t>1404-T2-TE-35</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - RRE H et RRE H2</t>
+          <t>BUSSY 2025 - VECTOR A</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>2192</v>
+        <v>1984</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>

--- a/dist/Datas/Log/Log_export.xlsx
+++ b/dist/Datas/Log/Log_export.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,27 +517,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15623</v>
+        <v>11821</v>
       </c>
       <c r="B2" t="n">
-        <v>691</v>
+        <v>1280</v>
       </c>
       <c r="C2" t="n">
         <v>300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hervé</t>
+          <t>Sébastien</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ARRIBART</t>
+          <t>GUYENNET</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Herve.Arribart@fr.toyota-industries.eu</t>
+          <t>Sebastien.GUYENNET@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -547,70 +547,70 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VECTOR A</t>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>VECTOR A</t>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1404-T2-TE-35</t>
+          <t>1404-T2-TE-61</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BUSSY 2025 - VECTOR A</t>
+          <t>CARQUEFOU 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>1984</v>
+        <v>2011</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-09-09 13:30</t>
+          <t>2025-09-01 13:30</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-09-12 12:00</t>
+          <t>2025-09-02 17:30</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17694</v>
+        <v>11027</v>
       </c>
       <c r="B3" t="n">
-        <v>691</v>
+        <v>1280</v>
       </c>
       <c r="C3" t="n">
         <v>300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>François-Xavier</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ALMEIDA</t>
+          <t>LUBERT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Maxime.Almeida@fr.toyota-industries.eu</t>
+          <t>Francois-Xavier.Lubert@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -620,337 +620,118 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>VECTOR A</t>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VECTOR A</t>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1404-T2-TE-35</t>
+          <t>1404-T2-TE-61</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BUSSY 2025 - VECTOR A</t>
+          <t>CARQUEFOU 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>1984</v>
+        <v>2011</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-09-09 13:30</t>
+          <t>2025-09-01 13:30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-09-12 12:00</t>
+          <t>2025-09-02 17:30</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18929</v>
+        <v>11368</v>
       </c>
       <c r="B4" t="n">
-        <v>691</v>
+        <v>1280</v>
       </c>
       <c r="C4" t="n">
         <v>300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sylvain</t>
+          <t>Rémi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hurte</t>
+          <t>BOIZUMEAU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sylvain.Hurte@ch.toyota-industries.eu</t>
+          <t>r.boizumeau@clenet-manutentionindustrie.fr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Toyota Material Handling Schweiz AG</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VECTOR A</t>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VECTOR A</t>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1404-T2-TE-35</t>
+          <t>1404-T2-TE-61</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BUSSY 2025 - VECTOR A</t>
+          <t>CARQUEFOU 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>1984</v>
+        <v>2011</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-09-09 13:30</t>
+          <t>2025-09-01 13:30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-09-12 12:00</t>
+          <t>2025-09-02 17:30</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>17341</v>
-      </c>
-      <c r="B5" t="n">
-        <v>691</v>
-      </c>
-      <c r="C5" t="n">
-        <v>300</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Léo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SANNA</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Leo.Sanna@fr.toyota-industries.eu</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Toyota Material Handling France S.A.S.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>VECTOR A</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>VECTOR A</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1404-T2-TE-35</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>711</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>BUSSY 2025 - VECTOR A</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1984</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-09 13:30</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-12 12:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>17622</v>
-      </c>
-      <c r="B6" t="n">
-        <v>691</v>
-      </c>
-      <c r="C6" t="n">
-        <v>300</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Nicolas</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>QUENTIN</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Nicolas.QUENTIN@fr.toyota-industries.eu</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Toyota Material Handling France S.A.S.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>VECTOR A</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>VECTOR A</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1404-T2-TE-35</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>711</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>BUSSY 2025 - VECTOR A</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1984</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-09 13:30</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-12 12:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>17440</v>
-      </c>
-      <c r="B7" t="n">
-        <v>691</v>
-      </c>
-      <c r="C7" t="n">
-        <v>300</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Matthieu</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PAPETTI</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Matthieu.Papetti@fr.toyota-industries.eu</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Toyota Material Handling France S.A.S.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>VECTOR A</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>VECTOR A</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1404-T2-TE-35</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>711</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>BUSSY 2025 - VECTOR A</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1984</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-09 13:30</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-12 12:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/dist/Datas/Log/Log_export.xlsx
+++ b/dist/Datas/Log/Log_export.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,10 +514,25 @@
           <t>duration_in_hours</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>formateur</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>lieu</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11821</v>
+        <v>12061</v>
       </c>
       <c r="B2" t="n">
         <v>1280</v>
@@ -527,17 +542,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sébastien</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GUYENNET</t>
+          <t>RICARD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sebastien.GUYENNET@fr.toyota-industries.eu</t>
+          <t>Maxime.RICARD@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -561,36 +576,51 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
+          <t>BUSSY 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>2011</v>
+        <v>1999</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-09-01 13:30</t>
+          <t>2025-10-22 13:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-09-02 17:30</t>
+          <t>2025-10-23 17:00</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>12</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Didier RENARD</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11027</v>
+        <v>11812</v>
       </c>
       <c r="B3" t="n">
         <v>1280</v>
@@ -600,17 +630,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>François-Xavier</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LUBERT</t>
+          <t>DERRIEN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Francois-Xavier.Lubert@fr.toyota-industries.eu</t>
+          <t>Patrick.DERRIEN@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -634,36 +664,51 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
+          <t>BUSSY 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>2011</v>
+        <v>1999</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-09-01 13:30</t>
+          <t>2025-10-22 13:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-09-02 17:30</t>
+          <t>2025-10-23 17:00</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>12</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Didier RENARD</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11368</v>
+        <v>17341</v>
       </c>
       <c r="B4" t="n">
         <v>1280</v>
@@ -673,22 +718,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rémi</t>
+          <t>Léo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BOIZUMEAU</t>
+          <t>SANNA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>r.boizumeau@clenet-manutentionindustrie.fr</t>
+          <t>Leo.Sanna@fr.toyota-industries.eu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>Toyota Material Handling France S.A.S.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -707,31 +752,310 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CARQUEFOU 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
+          <t>BUSSY 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>2011</v>
+        <v>1999</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-09-01 13:30</t>
+          <t>2025-10-22 13:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-09-02 17:30</t>
+          <t>2025-10-23 17:00</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>12</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Didier RENARD</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>17862</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DEGOMBERT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Damien.Degombert@fr.toyota-industries.eu</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Toyota Material Handling France S.A.S.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1404-T2-TE-61</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>717</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>BUSSY 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1999</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-22 13:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-23 17:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Didier RENARD</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>11291</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>philippe</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>herscher</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>philippe.herscher@altodis.fr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ALTODIS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1404-T2-TE-61</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>717</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>BUSSY 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1999</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-22 13:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-23 17:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Didier RENARD</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>11299</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pierre</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>morel</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pierre.morel@altodis.fr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ALTODIS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1404-T2-TE-61</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>717</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>BUSSY 2025 - LITHIUM-ION TMHMS &amp; TMHMI</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1999</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-22 13:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-23 17:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>12</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Didier RENARD</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>BUSSY</t>
+        </is>
       </c>
     </row>
   </sheetData>
